--- a/artfynd/A 5235-2025 artfynd.xlsx
+++ b/artfynd/A 5235-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125876892</v>
       </c>
       <c r="B2" t="n">
-        <v>95927</v>
+        <v>95934</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 5235-2025 artfynd.xlsx
+++ b/artfynd/A 5235-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125876892</v>
       </c>
       <c r="B2" t="n">
-        <v>95934</v>
+        <v>95935</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 5235-2025 artfynd.xlsx
+++ b/artfynd/A 5235-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125876892</v>
       </c>
       <c r="B2" t="n">
-        <v>95935</v>
+        <v>95937</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 5235-2025 artfynd.xlsx
+++ b/artfynd/A 5235-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125876892</v>
       </c>
       <c r="B2" t="n">
-        <v>95937</v>
+        <v>95941</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 5235-2025 artfynd.xlsx
+++ b/artfynd/A 5235-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125876892</v>
       </c>
       <c r="B2" t="n">
-        <v>95941</v>
+        <v>95942</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 5235-2025 artfynd.xlsx
+++ b/artfynd/A 5235-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125876892</v>
       </c>
       <c r="B2" t="n">
-        <v>95942</v>
+        <v>95944</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 5235-2025 artfynd.xlsx
+++ b/artfynd/A 5235-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125876892</v>
       </c>
       <c r="B2" t="n">
-        <v>95944</v>
+        <v>95946</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 5235-2025 artfynd.xlsx
+++ b/artfynd/A 5235-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125876892</v>
       </c>
       <c r="B2" t="n">
-        <v>95946</v>
+        <v>95948</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 5235-2025 artfynd.xlsx
+++ b/artfynd/A 5235-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125876892</v>
       </c>
       <c r="B2" t="n">
-        <v>95948</v>
+        <v>95952</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 5235-2025 artfynd.xlsx
+++ b/artfynd/A 5235-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125876892</v>
       </c>
       <c r="B2" t="n">
-        <v>95952</v>
+        <v>95955</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 5235-2025 artfynd.xlsx
+++ b/artfynd/A 5235-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125876892</v>
       </c>
       <c r="B2" t="n">
-        <v>95955</v>
+        <v>95964</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 5235-2025 artfynd.xlsx
+++ b/artfynd/A 5235-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>127174250</v>
       </c>
       <c r="B3" t="n">
-        <v>109185</v>
+        <v>109260</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>127174605</v>
       </c>
       <c r="B4" t="n">
-        <v>95964</v>
+        <v>96039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>127174246</v>
       </c>
       <c r="B5" t="n">
-        <v>98384</v>
+        <v>98459</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>127174244</v>
       </c>
       <c r="B6" t="n">
-        <v>109185</v>
+        <v>109260</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>127174249</v>
       </c>
       <c r="B7" t="n">
-        <v>109185</v>
+        <v>109260</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>127174241</v>
       </c>
       <c r="B8" t="n">
-        <v>109185</v>
+        <v>109260</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 5235-2025 artfynd.xlsx
+++ b/artfynd/A 5235-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>127174250</v>
       </c>
       <c r="B3" t="n">
-        <v>109260</v>
+        <v>109266</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127174605</v>
+        <v>127174246</v>
       </c>
       <c r="B4" t="n">
-        <v>96039</v>
+        <v>98465</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,31 +913,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>219847</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>716766</v>
+        <v>716778</v>
       </c>
       <c r="R4" t="n">
-        <v>6375144</v>
+        <v>6375167</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -992,6 +992,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Kallbarrskog.</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1008,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127174246</v>
+        <v>127174605</v>
       </c>
       <c r="B5" t="n">
-        <v>98459</v>
+        <v>96045</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1019,31 +1024,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219847</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>58</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1052,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>716778</v>
+        <v>716766</v>
       </c>
       <c r="R5" t="n">
-        <v>6375167</v>
+        <v>6375144</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1098,11 +1103,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Kallbarrskog.</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1122,7 +1122,7 @@
         <v>127174244</v>
       </c>
       <c r="B6" t="n">
-        <v>109260</v>
+        <v>109266</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>127174249</v>
       </c>
       <c r="B7" t="n">
-        <v>109260</v>
+        <v>109266</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>127174241</v>
       </c>
       <c r="B8" t="n">
-        <v>109260</v>
+        <v>109266</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 5235-2025 artfynd.xlsx
+++ b/artfynd/A 5235-2025 artfynd.xlsx
@@ -902,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127174246</v>
+        <v>127174605</v>
       </c>
       <c r="B4" t="n">
-        <v>98465</v>
+        <v>96045</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,31 +913,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219847</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>58</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>716778</v>
+        <v>716766</v>
       </c>
       <c r="R4" t="n">
-        <v>6375167</v>
+        <v>6375144</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -992,11 +992,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Kallbarrskog.</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1013,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127174605</v>
+        <v>127174246</v>
       </c>
       <c r="B5" t="n">
-        <v>96045</v>
+        <v>98465</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1024,31 +1019,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>219847</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1057,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>716766</v>
+        <v>716778</v>
       </c>
       <c r="R5" t="n">
-        <v>6375144</v>
+        <v>6375167</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1103,6 +1098,11 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Kallbarrskog.</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">

--- a/artfynd/A 5235-2025 artfynd.xlsx
+++ b/artfynd/A 5235-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>127174250</v>
       </c>
       <c r="B3" t="n">
-        <v>109266</v>
+        <v>109267</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>127174605</v>
       </c>
       <c r="B4" t="n">
-        <v>96045</v>
+        <v>96046</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>127174246</v>
       </c>
       <c r="B5" t="n">
-        <v>98465</v>
+        <v>98466</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>127174244</v>
       </c>
       <c r="B6" t="n">
-        <v>109266</v>
+        <v>109267</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>127174249</v>
       </c>
       <c r="B7" t="n">
-        <v>109266</v>
+        <v>109267</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>127174241</v>
       </c>
       <c r="B8" t="n">
-        <v>109266</v>
+        <v>109267</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 5235-2025 artfynd.xlsx
+++ b/artfynd/A 5235-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>127174250</v>
       </c>
       <c r="B3" t="n">
-        <v>109267</v>
+        <v>109273</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>127174605</v>
       </c>
       <c r="B4" t="n">
-        <v>96046</v>
+        <v>96050</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>127174246</v>
       </c>
       <c r="B5" t="n">
-        <v>98466</v>
+        <v>98470</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>127174244</v>
       </c>
       <c r="B6" t="n">
-        <v>109267</v>
+        <v>109273</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>127174249</v>
       </c>
       <c r="B7" t="n">
-        <v>109267</v>
+        <v>109273</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>127174241</v>
       </c>
       <c r="B8" t="n">
-        <v>109267</v>
+        <v>109273</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 5235-2025 artfynd.xlsx
+++ b/artfynd/A 5235-2025 artfynd.xlsx
@@ -902,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127174605</v>
+        <v>127174246</v>
       </c>
       <c r="B4" t="n">
-        <v>96050</v>
+        <v>98470</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,31 +913,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>219847</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>716766</v>
+        <v>716778</v>
       </c>
       <c r="R4" t="n">
-        <v>6375144</v>
+        <v>6375167</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -992,6 +992,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Kallbarrskog.</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1008,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127174246</v>
+        <v>127174605</v>
       </c>
       <c r="B5" t="n">
-        <v>98470</v>
+        <v>96050</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1019,31 +1024,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219847</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>58</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1052,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>716778</v>
+        <v>716766</v>
       </c>
       <c r="R5" t="n">
-        <v>6375167</v>
+        <v>6375144</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1098,11 +1103,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Kallbarrskog.</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">

--- a/artfynd/A 5235-2025 artfynd.xlsx
+++ b/artfynd/A 5235-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>127174250</v>
       </c>
       <c r="B3" t="n">
-        <v>109273</v>
+        <v>109275</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>127174246</v>
       </c>
       <c r="B4" t="n">
-        <v>98470</v>
+        <v>98471</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>127174244</v>
       </c>
       <c r="B6" t="n">
-        <v>109273</v>
+        <v>109275</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>127174249</v>
       </c>
       <c r="B7" t="n">
-        <v>109273</v>
+        <v>109275</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>127174241</v>
       </c>
       <c r="B8" t="n">
-        <v>109273</v>
+        <v>109275</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 5235-2025 artfynd.xlsx
+++ b/artfynd/A 5235-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>127174250</v>
       </c>
       <c r="B3" t="n">
-        <v>109275</v>
+        <v>109277</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127174246</v>
+        <v>127174605</v>
       </c>
       <c r="B4" t="n">
-        <v>98471</v>
+        <v>96052</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,31 +913,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219847</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>58</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>716778</v>
+        <v>716766</v>
       </c>
       <c r="R4" t="n">
-        <v>6375167</v>
+        <v>6375144</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -992,11 +992,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Kallbarrskog.</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1013,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127174605</v>
+        <v>127174246</v>
       </c>
       <c r="B5" t="n">
-        <v>96050</v>
+        <v>98473</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1024,31 +1019,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>219847</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1057,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>716766</v>
+        <v>716778</v>
       </c>
       <c r="R5" t="n">
-        <v>6375144</v>
+        <v>6375167</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1103,6 +1098,11 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Kallbarrskog.</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1122,7 +1122,7 @@
         <v>127174244</v>
       </c>
       <c r="B6" t="n">
-        <v>109275</v>
+        <v>109277</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>127174249</v>
       </c>
       <c r="B7" t="n">
-        <v>109275</v>
+        <v>109277</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>127174241</v>
       </c>
       <c r="B8" t="n">
-        <v>109275</v>
+        <v>109277</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 5235-2025 artfynd.xlsx
+++ b/artfynd/A 5235-2025 artfynd.xlsx
@@ -902,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127174605</v>
+        <v>127174246</v>
       </c>
       <c r="B4" t="n">
-        <v>96052</v>
+        <v>98473</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,31 +913,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>219847</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>716766</v>
+        <v>716778</v>
       </c>
       <c r="R4" t="n">
-        <v>6375144</v>
+        <v>6375167</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -992,6 +992,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Kallbarrskog.</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1008,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127174246</v>
+        <v>127174605</v>
       </c>
       <c r="B5" t="n">
-        <v>98473</v>
+        <v>96052</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1019,31 +1024,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219847</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>58</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1052,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>716778</v>
+        <v>716766</v>
       </c>
       <c r="R5" t="n">
-        <v>6375167</v>
+        <v>6375144</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1098,11 +1103,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Kallbarrskog.</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">

--- a/artfynd/A 5235-2025 artfynd.xlsx
+++ b/artfynd/A 5235-2025 artfynd.xlsx
@@ -902,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127174246</v>
+        <v>127174605</v>
       </c>
       <c r="B4" t="n">
-        <v>98473</v>
+        <v>96052</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,31 +913,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219847</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>58</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>716778</v>
+        <v>716766</v>
       </c>
       <c r="R4" t="n">
-        <v>6375167</v>
+        <v>6375144</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -992,11 +992,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Kallbarrskog.</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1013,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127174605</v>
+        <v>127174246</v>
       </c>
       <c r="B5" t="n">
-        <v>96052</v>
+        <v>98473</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1024,31 +1019,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>219847</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1057,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>716766</v>
+        <v>716778</v>
       </c>
       <c r="R5" t="n">
-        <v>6375144</v>
+        <v>6375167</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1103,6 +1098,11 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Kallbarrskog.</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">

--- a/artfynd/A 5235-2025 artfynd.xlsx
+++ b/artfynd/A 5235-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>127174250</v>
       </c>
       <c r="B3" t="n">
-        <v>109277</v>
+        <v>109283</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>127174605</v>
       </c>
       <c r="B4" t="n">
-        <v>96052</v>
+        <v>96058</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>127174246</v>
       </c>
       <c r="B5" t="n">
-        <v>98473</v>
+        <v>98479</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>127174244</v>
       </c>
       <c r="B6" t="n">
-        <v>109277</v>
+        <v>109283</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>127174249</v>
       </c>
       <c r="B7" t="n">
-        <v>109277</v>
+        <v>109283</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>127174241</v>
       </c>
       <c r="B8" t="n">
-        <v>109277</v>
+        <v>109283</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 5235-2025 artfynd.xlsx
+++ b/artfynd/A 5235-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>127174250</v>
       </c>
       <c r="B3" t="n">
-        <v>109283</v>
+        <v>109286</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127174605</v>
+        <v>127174246</v>
       </c>
       <c r="B4" t="n">
-        <v>96058</v>
+        <v>98482</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,31 +913,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>219847</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>716766</v>
+        <v>716778</v>
       </c>
       <c r="R4" t="n">
-        <v>6375144</v>
+        <v>6375167</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -992,6 +992,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Kallbarrskog.</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1008,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127174246</v>
+        <v>127174605</v>
       </c>
       <c r="B5" t="n">
-        <v>98479</v>
+        <v>96061</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1019,31 +1024,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219847</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>58</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1052,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>716778</v>
+        <v>716766</v>
       </c>
       <c r="R5" t="n">
-        <v>6375167</v>
+        <v>6375144</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1098,11 +1103,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Kallbarrskog.</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1122,7 +1122,7 @@
         <v>127174244</v>
       </c>
       <c r="B6" t="n">
-        <v>109283</v>
+        <v>109286</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>127174249</v>
       </c>
       <c r="B7" t="n">
-        <v>109283</v>
+        <v>109286</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>127174241</v>
       </c>
       <c r="B8" t="n">
-        <v>109283</v>
+        <v>109286</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 5235-2025 artfynd.xlsx
+++ b/artfynd/A 5235-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>127174250</v>
       </c>
       <c r="B3" t="n">
-        <v>109286</v>
+        <v>109294</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127174246</v>
+        <v>127174605</v>
       </c>
       <c r="B4" t="n">
-        <v>98482</v>
+        <v>96069</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,31 +913,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219847</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>58</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>716778</v>
+        <v>716766</v>
       </c>
       <c r="R4" t="n">
-        <v>6375167</v>
+        <v>6375144</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -992,11 +992,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Kallbarrskog.</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1013,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127174605</v>
+        <v>127174246</v>
       </c>
       <c r="B5" t="n">
-        <v>96061</v>
+        <v>98490</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1024,31 +1019,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>219847</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1057,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>716766</v>
+        <v>716778</v>
       </c>
       <c r="R5" t="n">
-        <v>6375144</v>
+        <v>6375167</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1103,6 +1098,11 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Kallbarrskog.</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1122,7 +1122,7 @@
         <v>127174244</v>
       </c>
       <c r="B6" t="n">
-        <v>109286</v>
+        <v>109294</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>127174249</v>
       </c>
       <c r="B7" t="n">
-        <v>109286</v>
+        <v>109294</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>127174241</v>
       </c>
       <c r="B8" t="n">
-        <v>109286</v>
+        <v>109294</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 5235-2025 artfynd.xlsx
+++ b/artfynd/A 5235-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>127174250</v>
       </c>
       <c r="B3" t="n">
-        <v>109294</v>
+        <v>109295</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>127174605</v>
       </c>
       <c r="B4" t="n">
-        <v>96069</v>
+        <v>96070</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>127174246</v>
       </c>
       <c r="B5" t="n">
-        <v>98490</v>
+        <v>98491</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>127174244</v>
       </c>
       <c r="B6" t="n">
-        <v>109294</v>
+        <v>109295</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>127174249</v>
       </c>
       <c r="B7" t="n">
-        <v>109294</v>
+        <v>109295</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>127174241</v>
       </c>
       <c r="B8" t="n">
-        <v>109294</v>
+        <v>109295</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 5235-2025 artfynd.xlsx
+++ b/artfynd/A 5235-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>127174250</v>
       </c>
       <c r="B3" t="n">
-        <v>109295</v>
+        <v>109260</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>127174605</v>
       </c>
       <c r="B4" t="n">
-        <v>96070</v>
+        <v>96039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>127174246</v>
       </c>
       <c r="B5" t="n">
-        <v>98491</v>
+        <v>98459</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>127174244</v>
       </c>
       <c r="B6" t="n">
-        <v>109295</v>
+        <v>109260</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>127174249</v>
       </c>
       <c r="B7" t="n">
-        <v>109295</v>
+        <v>109260</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>127174241</v>
       </c>
       <c r="B8" t="n">
-        <v>109295</v>
+        <v>109260</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 5235-2025 artfynd.xlsx
+++ b/artfynd/A 5235-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125876892</v>
       </c>
       <c r="B2" t="n">
-        <v>95964</v>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -786,42 +786,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127174250</v>
+        <v>127174605</v>
       </c>
       <c r="B3" t="n">
-        <v>109295</v>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220299</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>58</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>716825</v>
+        <v>716766</v>
       </c>
       <c r="R3" t="n">
-        <v>6375202</v>
+        <v>6375144</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -868,11 +868,6 @@
           <t>2025-06-21</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Minsta antal.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -881,11 +876,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Kallbarrskog.</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -902,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127174605</v>
+        <v>127174246</v>
       </c>
       <c r="B4" t="n">
-        <v>96070</v>
+        <v>99142</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,31 +903,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>219847</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -946,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>716766</v>
+        <v>716778</v>
       </c>
       <c r="R4" t="n">
-        <v>6375144</v>
+        <v>6375167</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -992,6 +982,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Kallbarrskog.</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1008,54 +1003,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127174246</v>
+        <v>127174241</v>
       </c>
       <c r="B5" t="n">
-        <v>98491</v>
+        <v>110078</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hartviks 1:40 (6), Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>716778</v>
+        <v>716744</v>
       </c>
       <c r="R5" t="n">
-        <v>6375167</v>
+        <v>6375150</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1101,7 +1087,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Kallbarrskog.</t>
+          <t>Tallsumpskog.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1122,7 +1108,7 @@
         <v>127174244</v>
       </c>
       <c r="B6" t="n">
-        <v>109295</v>
+        <v>110078</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1224,7 @@
         <v>127174249</v>
       </c>
       <c r="B7" t="n">
-        <v>109295</v>
+        <v>110078</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,10 +1337,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127174241</v>
+        <v>127174250</v>
       </c>
       <c r="B8" t="n">
-        <v>109295</v>
+        <v>110078</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1379,17 +1365,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hartviks 1:40 (6), Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>716744</v>
+        <v>716825</v>
       </c>
       <c r="R8" t="n">
-        <v>6375150</v>
+        <v>6375202</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1424,6 +1419,11 @@
           <t>2025-06-21</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Minsta antal.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Tallsumpskog.</t>
+          <t>Kallbarrskog.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>

--- a/artfynd/A 5235-2025 artfynd.xlsx
+++ b/artfynd/A 5235-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -892,57 +892,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127174246</v>
+        <v>134671119</v>
       </c>
       <c r="B4" t="n">
-        <v>99142</v>
+        <v>43472</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219847</v>
+        <v>101242</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hartviks 1:40 (6), Gtl</t>
+          <t>Brandmyr, Brandmyr, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>716778</v>
+        <v>716802</v>
       </c>
       <c r="R4" t="n">
-        <v>6375167</v>
+        <v>6375449</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -966,12 +957,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-21</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-21</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -982,66 +983,70 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Kallbarrskog.</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127174241</v>
+        <v>127174246</v>
       </c>
       <c r="B5" t="n">
-        <v>110078</v>
+        <v>99142</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hartviks 1:40 (6), Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>716744</v>
+        <v>716778</v>
       </c>
       <c r="R5" t="n">
-        <v>6375150</v>
+        <v>6375167</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1087,7 +1092,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Tallsumpskog.</t>
+          <t>Kallbarrskog.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1105,7 +1110,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127174244</v>
+        <v>127174241</v>
       </c>
       <c r="B6" t="n">
         <v>110078</v>
@@ -1133,26 +1138,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hartviks 1:40 (6), Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>716770</v>
+        <v>716744</v>
       </c>
       <c r="R6" t="n">
-        <v>6375159</v>
+        <v>6375150</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1185,11 +1181,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-06-21</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Även spridd.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1221,7 +1212,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127174249</v>
+        <v>127174244</v>
       </c>
       <c r="B7" t="n">
         <v>110078</v>
@@ -1251,7 +1242,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1265,10 +1256,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>716791</v>
+        <v>716770</v>
       </c>
       <c r="R7" t="n">
-        <v>6375179</v>
+        <v>6375159</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1305,7 +1296,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Minsta antal.</t>
+          <t>Även spridd.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1319,7 +1310,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Kallbarrskog.</t>
+          <t>Tallsumpskog.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1337,7 +1328,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127174250</v>
+        <v>127174249</v>
       </c>
       <c r="B8" t="n">
         <v>110078</v>
@@ -1367,7 +1358,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1381,10 +1372,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>716825</v>
+        <v>716791</v>
       </c>
       <c r="R8" t="n">
-        <v>6375202</v>
+        <v>6375179</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1450,6 +1441,122 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>127174250</v>
+      </c>
+      <c r="B9" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hartviks 1:40 (6), Gtl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>716825</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6375202</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ganthem</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Minsta antal.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Kallbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 5235-2025 artfynd.xlsx
+++ b/artfynd/A 5235-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125876892</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,6 +899,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127174605</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,6 +1011,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134671119</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1107,6 +1127,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127174246</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1209,6 +1234,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127174241</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1325,6 +1355,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127174244</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1441,6 +1476,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127174249</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1557,8 +1597,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127174250</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>